--- a/v3/templates/export-base.xlsx
+++ b/v3/templates/export-base.xlsx
@@ -755,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C47"/>
+  <dimension ref="B1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -763,6 +763,7 @@
     <col width="96" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -777,6 +778,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="20" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -849,6 +851,7 @@
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13" ht="20" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -893,6 +896,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="20" customHeight="1">
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -932,6 +936,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="20" customHeight="1">
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -990,6 +995,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30" ht="20" customHeight="1">
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -1037,6 +1043,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37" ht="20" customHeight="1">
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -1090,7 +1097,7 @@
     <row r="44">
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>7. 引用文件編號若有填，必須存在於系統「參考文件」。</t>
+          <t>7. 引用文件編號若在目前標案的「參考文件」找不到（例如從別的標案匯出的檔案），匯入時略過、不檢核，該項目匯入後不引用文件。</t>
         </is>
       </c>
     </row>
@@ -1114,9 +1121,9 @@
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B44:C44"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B47:C47"/>
     <mergeCell ref="B3:C3"/>
@@ -7861,7 +7868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O300"/>
+  <dimension ref="A1:N300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
